--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_05-02-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_05-02-2026.xlsx
@@ -533,17 +533,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£10.55</t>
+          <t>£10.48</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.55</t>
+          <t>£10.48</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.55</t>
+          <t>£10.48</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>£10.48</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -625,17 +625,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£12.09</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£12.09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£12.09</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>£12.15</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -717,17 +717,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£15.56</t>
+          <t>£15.26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£15.56</t>
+          <t>£15.26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£15.56</t>
+          <t>£15.26</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>£15.26</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -809,17 +809,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£16.17</t>
+          <t>£15.86</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£16.17</t>
+          <t>£15.86</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£16.17</t>
+          <t>£15.86</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>£15.86</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£19.76</t>
+          <t>£19.71</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£19.76</t>
+          <t>£19.71</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£19.76</t>
+          <t>£19.71</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>£19.75</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>£22.06</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>£22.13</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£25.04</t>
+          <t>£25.09</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£25.04</t>
+          <t>£25.09</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£25.04</t>
+          <t>£25.09</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>£25.47</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>£27.69</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>£27.25</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1453,17 +1453,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£35.30</t>
+          <t>£33.99</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£35.30</t>
+          <t>£33.99</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£35.30</t>
+          <t>£33.99</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>£33.99</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>£33.38</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>£41.12</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>£40.99</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>£42.35</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1821,17 +1821,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£41.67</t>
+          <t>£40.68</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£41.67</t>
+          <t>£40.68</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£41.67</t>
+          <t>£40.68</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>£40.68</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>£779.88</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>£1019.88</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£29.30</t>
+          <t>£28.53</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>£29.30</t>
+          <t>£28.53</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>£29.30</t>
+          <t>£28.53</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>£28.55</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2189,17 +2189,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£35.54</t>
+          <t>£34.95</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>£35.54</t>
+          <t>£34.95</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>£35.54</t>
+          <t>£34.95</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>£34.99</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>£31.75</t>
+          <t>£32.69</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>£37.40</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>£42.55</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>£48.17</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>£47.58</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>£1,016.40</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>£44.58</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>£47.08</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>£1267.2</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>£1408.0</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>£1377.12</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>£1408.0</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
